--- a/docs/oc-mensuales/gas-licuado-de-petroleo/dic-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>151.71</v>
+        <v>149.75</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1894.54</v>
+        <v>1870.05</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>90.28</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5297.58</v>
+        <v>5229.11</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4340.81</v>
+        <v>4284.7</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5876.07</v>
+        <v>5800.12</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3845.77</v>
+        <v>3796.06</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>285.24</v>
+        <v>281.55</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>709.5599999999999</v>
+        <v>700.39</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>330.44</v>
+        <v>326.17</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>446.56</v>
+        <v>440.79</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4624.07</v>
+        <v>4564.3</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>250.95</v>
+        <v>247.7</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>462.93</v>
+        <v>456.94</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>141.84</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>325.24</v>
+        <v>321.04</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4559.12</v>
+        <v>4500.19</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>385.77</v>
+        <v>380.79</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>348.75</v>
+        <v>344.24</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>214.97</v>
+        <v>212.19</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1124.3</v>
+        <v>1109.77</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>37.34</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>142.62</v>
+        <v>140.78</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8149.39</v>
+        <v>8044.06</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1719.74</v>
+        <v>1697.51</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>66.37</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>516.96</v>
+        <v>510.28</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>397.19</v>
+        <v>392.05</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>359.53</v>
+        <v>354.89</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>494.28</v>
+        <v>487.89</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>172.67</v>
+        <v>170.43</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>284.59</v>
+        <v>280.91</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>482.53</v>
+        <v>476.29</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>145.02</v>
+        <v>143.15</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4065.54</v>
+        <v>4012.99</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>437.11</v>
+        <v>431.46</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>829.99</v>
+        <v>819.27</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>177.69</v>
+        <v>175.39</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>42.99</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>574.25</v>
+        <v>566.83</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>568.92</v>
+        <v>561.5599999999999</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>475.4</v>
+        <v>469.25</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3972.08</v>
+        <v>3920.74</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>66.37</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>455.91</v>
+        <v>450.02</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2745.36</v>
+        <v>2709.88</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>428.12</v>
+        <v>422.58</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>528.52</v>
+        <v>521.6900000000001</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3772.8</v>
+        <v>3724.88</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>876.75</v>
+        <v>865.62</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1650.29</v>
+        <v>1629.33</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17197.38</v>
+        <v>16978.93</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8934.17</v>
+        <v>8820.68</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1928.86</v>
+        <v>1904.36</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>683.87</v>
+        <v>675.1799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7.31</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1269.65</v>
+        <v>1253.52</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2478.29</v>
+        <v>2446.81</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>893.12</v>
+        <v>881.78</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>70.34</v>
+        <v>69.44</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>820.64</v>
+        <v>810.22</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>432.21</v>
+        <v>426.72</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>547.09</v>
+        <v>540.15</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>505.01</v>
+        <v>498.6</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>18950.87</v>
+        <v>18710.15</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3236.07</v>
+        <v>3194.96</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>621.91</v>
+        <v>614.01</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1157.32</v>
+        <v>1142.62</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2376.98</v>
+        <v>2346.79</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1550.88</v>
+        <v>1531.18</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1442.64</v>
+        <v>1424.32</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>292.25</v>
+        <v>288.54</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>6415.37</v>
+        <v>6333.88</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>406.81</v>
+        <v>401.65</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>449.42</v>
+        <v>443.71</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>399.85</v>
+        <v>394.77</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>493.06</v>
+        <v>486.8</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>178.62</v>
+        <v>176.36</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>227.96</v>
+        <v>225.06</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1582.99</v>
+        <v>1562.88</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>280.56</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>955.99</v>
+        <v>943.84</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>65.15000000000001</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1240.7</v>
+        <v>1224.95</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>151.96</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>126.4</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>836.49</v>
+        <v>825.86</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>413.57</v>
+        <v>408.32</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2284.3</v>
+        <v>2255.28</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>495.66</v>
+        <v>489.36</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>598.66</v>
+        <v>591.0599999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>595.41</v>
+        <v>587.85</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>248.09</v>
+        <v>245.62</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2933.72</v>
+        <v>2904.53</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>246.02</v>
+        <v>243.58</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>164.69</v>
+        <v>163.05</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>507.87</v>
+        <v>502.82</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1278.21</v>
+        <v>1265.49</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>125.47</v>
+        <v>124.22</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>420.84</v>
+        <v>416.65</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>137.31</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>168.34</v>
+        <v>166.66</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>578.66</v>
+        <v>572.9</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>147.85</v>
+        <v>146.38</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>155.09</v>
+        <v>153.55</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2170.32</v>
+        <v>2148.73</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>988.85</v>
+        <v>979.01</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>356.85</v>
+        <v>353.3</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>809.21</v>
+        <v>801.16</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>388.47</v>
+        <v>384.61</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>564.24</v>
+        <v>558.63</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>12266.55</v>
+        <v>12144.51</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>331.87</v>
+        <v>328.57</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>496.18</v>
+        <v>491.24</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>587.61</v>
+        <v>581.76</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2081.74</v>
+        <v>2061.03</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>294.69</v>
+        <v>291.75</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>150.93</v>
+        <v>149.43</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>195.35</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>148.2</v>
+        <v>146.73</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>555.28</v>
+        <v>549.75</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2131.96</v>
+        <v>2110.74</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1260.4</v>
+        <v>1247.86</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>494.36</v>
+        <v>489.44</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>760.63</v>
+        <v>753.0700000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>749.41</v>
+        <v>741.95</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>382.93</v>
+        <v>379.12</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>319.14</v>
+        <v>315.96</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>285.5</v>
+        <v>282.66</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>90.14</v>
+        <v>89.25</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>174.37</v>
+        <v>172.64</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>190.37</v>
+        <v>188.48</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>334.6</v>
+        <v>331.27</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>737.77</v>
+        <v>730.4299999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>669.1900000000001</v>
+        <v>662.53</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>155.09</v>
+        <v>153.55</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>858.89</v>
+        <v>850.35</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>627.37</v>
+        <v>621.12</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>348.75</v>
+        <v>345.28</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>435.63</v>
+        <v>431.29</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>533.0700000000001</v>
+        <v>531.16</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>448.42</v>
+        <v>446.81</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1121.76</v>
+        <v>1117.74</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>901.4299999999999</v>
+        <v>898.2</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>327.32</v>
+        <v>326.15</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>294.27</v>
+        <v>293.21</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2539.34</v>
+        <v>2530.24</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1586.64</v>
+        <v>1580.95</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2671.27</v>
+        <v>2661.69</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>366.81</v>
+        <v>365.49</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>167.82</v>
+        <v>167.22</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>246.27</v>
+        <v>245.39</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>528.39</v>
+        <v>526.5</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>419.54</v>
+        <v>418.04</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>92.94</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>532.4</v>
+        <v>530.49</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>17627.1</v>
+        <v>17563.9</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>699.61</v>
+        <v>697.1</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1975.09</v>
+        <v>1968.01</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>108.17</v>
+        <v>107.78</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>320.38</v>
+        <v>319.23</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>192.23</v>
+        <v>191.54</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>283.91</v>
+        <v>282.89</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4719.88</v>
+        <v>4702.95</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>788.52</v>
+        <v>785.6900000000001</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>277.31</v>
+        <v>276.32</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>198.08</v>
+        <v>197.37</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>355.38</v>
+        <v>354.1</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>262.28</v>
+        <v>261.34</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>4702</v>
+        <v>4685.14</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2734.5</v>
+        <v>2724.69</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>8203.5</v>
+        <v>8174.08</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>852.77</v>
+        <v>849.71</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>369.93</v>
+        <v>368.6</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>141.84</v>
+        <v>141.33</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>31455.83</v>
+        <v>31343.03</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>41700.55</v>
+        <v>41551.02</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1402.81</v>
+        <v>1397.78</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>26318.74</v>
+        <v>26224.37</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>455.91</v>
+        <v>454.28</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>30475.64</v>
+        <v>30366.36</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>137.94</v>
+        <v>137.64</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>143.01</v>
+        <v>142.7</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>140.28</v>
+        <v>139.98</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1409.04</v>
+        <v>1405.99</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>17680.86</v>
+        <v>17642.59</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1874.31</v>
+        <v>1870.25</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>433.83</v>
+        <v>432.89</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>9056.940000000001</v>
+        <v>9037.34</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1049.51</v>
+        <v>1047.24</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>112.61</v>
+        <v>112.37</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>714.8</v>
+        <v>713.25</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>587.62</v>
+        <v>586.35</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1675.58</v>
+        <v>1671.95</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4670.22</v>
+        <v>4660.11</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>15359.72</v>
+        <v>15326.48</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>279</v>
+        <v>278.4</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3032.2</v>
+        <v>3025.64</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>695.5599999999999</v>
+        <v>694.05</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>704.85</v>
+        <v>703.33</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>900.91</v>
+        <v>898.96</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>489.29</v>
+        <v>488.23</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>227.13</v>
+        <v>226.64</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1577.89</v>
+        <v>1574.48</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>146.84</v>
+        <v>146.52</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1637.06</v>
+        <v>1633.52</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>367.66</v>
+        <v>366.86</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>462.93</v>
+        <v>461.92</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>578.66</v>
+        <v>577.41</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>283.91</v>
+        <v>283.3</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2081.74</v>
+        <v>2077.23</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>282.12</v>
+        <v>281.51</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3668.08</v>
+        <v>3660.14</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1458.92</v>
+        <v>1455.76</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>161.79</v>
+        <v>161.44</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>164.18</v>
+        <v>163.83</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1288.5</v>
+        <v>1285.72</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1188.49</v>
+        <v>1185.92</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2517.26</v>
+        <v>2511.81</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>435.96</v>
+        <v>435.02</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>980.67</v>
+        <v>978.54</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>986.51</v>
+        <v>984.38</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>195.48</v>
+        <v>195.06</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1110.15</v>
+        <v>1107.75</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>320.03</v>
+        <v>319.34</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>952.76</v>
+        <v>950.7</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>609.4400000000001</v>
+        <v>608.12</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3292.7</v>
+        <v>3285.57</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>153.2</v>
+        <v>152.56</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3005.68</v>
+        <v>2993.08</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>566.9400000000001</v>
+        <v>564.5700000000001</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2573.66</v>
+        <v>2562.87</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>362.27</v>
+        <v>360.75</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>2573.74</v>
+        <v>2562.95</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4297.72</v>
+        <v>4279.7</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>218.42</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1379.43</v>
+        <v>1373.64</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1217.78</v>
+        <v>1212.67</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>34968.06</v>
+        <v>34821.46</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>346.46</v>
+        <v>345.01</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4477.29</v>
+        <v>4458.52</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2225.24</v>
+        <v>2215.92</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>186</v>
+        <v>185.22</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4951.14</v>
+        <v>4930.38</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>660.49</v>
+        <v>657.72</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>51.9</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>10911.5</v>
+        <v>10865.76</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>36822.52</v>
+        <v>36668.15</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>130.33</v>
+        <v>129.78</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>3871.48</v>
+        <v>3855.25</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>792.59</v>
+        <v>789.26</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>179.77</v>
+        <v>179.01</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>264.2</v>
+        <v>263.09</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1153.69</v>
+        <v>1148.86</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>157.43</v>
+        <v>156.77</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>264.2</v>
+        <v>263.09</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>629.7</v>
+        <v>627.0599999999999</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1345.68</v>
+        <v>1340.03</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>255.04</v>
+        <v>253.97</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>157.43</v>
+        <v>156.77</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>125.86</v>
+        <v>125.34</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>83.23</v>
+        <v>82.88</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>219.51</v>
+        <v>218.59</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>174.88</v>
+        <v>174.15</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>968.74</v>
+        <v>964.67</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>827.0700000000001</v>
+        <v>823.6</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>206.09</v>
+        <v>205.22</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1587.77</v>
+        <v>1581.11</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1117.31</v>
+        <v>1112.63</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>1371.24</v>
+        <v>1365.5</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1098.87</v>
+        <v>1094.26</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>270.04</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>945.63</v>
+        <v>941.66</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>707.46</v>
+        <v>704.5</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>270.04</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>694.39</v>
+        <v>691.48</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>161.06</v>
+        <v>160.39</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>503.32</v>
+        <v>501.21</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1574.26</v>
+        <v>1567.66</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>413.05</v>
+        <v>411.32</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>615.6799999999999</v>
+        <v>613.1</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>684.52</v>
+        <v>681.65</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>189.6</v>
+        <v>188.8</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>189.6</v>
+        <v>188.8</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2013.29</v>
+        <v>2004.85</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>57.95</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3190.74</v>
+        <v>3177.36</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>19571.76</v>
+        <v>19489.71</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>231.81</v>
+        <v>230.84</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>959.04</v>
+        <v>955.02</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>117.47</v>
+        <v>116.98</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>70.14</v>
+        <v>69.84999999999999</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1352.81</v>
+        <v>1347.14</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1418.39</v>
+        <v>1412.45</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3223.34</v>
+        <v>3209.83</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>167.82</v>
+        <v>167.11</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>223.41</v>
+        <v>220.82</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>13453.16</v>
+        <v>13297.47</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4132.54</v>
+        <v>4084.71</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5350.79</v>
+        <v>5288.86</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3483.53</v>
+        <v>3443.22</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1302.01</v>
+        <v>1286.94</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>293.68</v>
+        <v>290.28</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>433.79</v>
+        <v>428.77</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>551.77</v>
+        <v>545.39</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>5454.06</v>
+        <v>5390.94</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>10722.38</v>
+        <v>10598.29</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>110.08</v>
+        <v>108.81</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2262.95</v>
+        <v>2236.76</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3992.34</v>
+        <v>3946.14</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>426.26</v>
+        <v>421.33</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>122.36</v>
+        <v>120.94</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>600.4299999999999</v>
+        <v>593.48</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1036.13</v>
+        <v>1024.14</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3651.3</v>
+        <v>3609.04</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>609.35</v>
+        <v>602.3</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>704.52</v>
+        <v>696.37</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>132.1</v>
+        <v>130.57</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>2415.95</v>
+        <v>2387.99</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>4828.01</v>
+        <v>4772.14</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>1390.95</v>
+        <v>1374.85</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>27686.09</v>
+        <v>27365.67</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>421.22</v>
+        <v>416.35</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2022.74</v>
+        <v>1999.33</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>115.73</v>
+        <v>114.39</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>433.46</v>
+        <v>428.45</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>817.6799999999999</v>
+        <v>808.22</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>267.57</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>721.15</v>
+        <v>712.8</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>509.49</v>
+        <v>503.59</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>32246.09</v>
+        <v>31872.91</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>56.11</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>381.02</v>
+        <v>376.61</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>12438.54</v>
+        <v>12294.59</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>125.16</v>
+        <v>123.71</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1896</v>
+        <v>1874.06</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1356.05</v>
+        <v>1340.35</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>81.56999999999999</v>
+        <v>80.63</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>328.08</v>
+        <v>324.28</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2092.52</v>
+        <v>2068.3</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>629.3099999999999</v>
+        <v>622.03</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>145.74</v>
+        <v>144.05</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>2535.64</v>
+        <v>2506.29</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1013.14</v>
+        <v>1001.41</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>419.54</v>
+        <v>414.69</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2802.17</v>
+        <v>2769.74</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>724.78</v>
+        <v>718.64</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>2627.67</v>
+        <v>2605.41</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>750.76</v>
+        <v>744.4</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>2403.22</v>
+        <v>2382.86</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>196.13</v>
+        <v>194.47</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>463.97</v>
+        <v>460.04</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>108.62</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>17095.67</v>
+        <v>16950.86</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>1313.83</v>
+        <v>1302.7</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>15747.81</v>
+        <v>15614.41</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3725.75</v>
+        <v>3694.19</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1755.26</v>
+        <v>1740.39</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>279</v>
+        <v>276.64</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>207.57</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>6699.54</v>
+        <v>6642.79</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>970.6</v>
+        <v>962.38</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>305.5</v>
+        <v>302.91</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>15826.44</v>
+        <v>15692.38</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>445.78</v>
+        <v>442</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>15538.89</v>
+        <v>15407.27</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>17275.31</v>
+        <v>17128.97</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>98.06999999999999</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>2536.74</v>
+        <v>2515.25</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>132.1</v>
+        <v>130.98</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>336.47</v>
+        <v>333.62</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>78.45</v>
+        <v>77.79000000000001</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>284.05</v>
+        <v>281.64</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1405.79</v>
+        <v>1393.89</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>6661.93</v>
+        <v>6605.5</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>98.06999999999999</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>563.0700000000001</v>
+        <v>558.3</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>120.8</v>
+        <v>119.77</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>4455.21</v>
+        <v>4417.47</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>178.77</v>
+        <v>177.26</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>419.54</v>
+        <v>415.99</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1126.14</v>
+        <v>1116.6</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>12893.16</v>
+        <v>12783.95</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>10460.72</v>
+        <v>10372.11</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>1091.66</v>
+        <v>1082.42</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1650.9</v>
+        <v>1636.91</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>41.95</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>419.54</v>
+        <v>415.99</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>402.66</v>
+        <v>399.25</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>930.01</v>
+        <v>922.13</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>280.56</v>
+        <v>278.18</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>668.28</v>
+        <v>662.62</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>762.04</v>
+        <v>755.58</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>1834.04</v>
+        <v>1818.5</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1708.5</v>
+        <v>1707.12</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>953.71</v>
+        <v>952.95</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>201.07</v>
+        <v>200.91</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1114.45</v>
+        <v>1113.56</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>150.8</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>150.8</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>174.57</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>124.69</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>1200.18</v>
+        <v>1199.21</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>14808.45</v>
+        <v>14796.54</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>150.8</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>7749.06</v>
+        <v>7742.83</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>10919.48</v>
+        <v>10910.7</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>662.12</v>
+        <v>661.59</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1716.69</v>
+        <v>1715.31</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>838.36</v>
+        <v>837.6900000000001</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>6398.1</v>
+        <v>6392.96</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>83.95999999999999</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>4211.99</v>
+        <v>4208.61</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>4021.52</v>
+        <v>4018.29</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>124.69</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>5816.05</v>
+        <v>5811.38</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>4156.47</v>
+        <v>4153.12</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>415.65</v>
+        <v>415.31</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3086.18</v>
+        <v>3083.7</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>485.59</v>
+        <v>485.2</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>10281.02</v>
+        <v>10272.75</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>117.68</v>
+        <v>117.59</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1192.13</v>
+        <v>1191.17</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>131.34</v>
+        <v>131.24</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1492.43</v>
+        <v>1491.23</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3082.28</v>
+        <v>3079.8</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>1724.93</v>
+        <v>1723.55</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>440.33</v>
+        <v>439.97</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>257.18</v>
+        <v>256.97</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>629.3099999999999</v>
+        <v>628.8099999999999</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>87.29000000000001</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1845.28</v>
+        <v>1843.79</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>271.07</v>
+        <v>270.86</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>156.26</v>
+        <v>156.13</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>643.73</v>
+        <v>643.22</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1361.34</v>
+        <v>1360.25</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>369.3</v>
+        <v>369.01</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>124.69</v>
+        <v>124.59</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>600.61</v>
+        <v>600.13</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2387.14</v>
+        <v>2396.3</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>415.65</v>
+        <v>417.24</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>707.25</v>
+        <v>709.96</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>481.89</v>
+        <v>483.74</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>1427.75</v>
+        <v>1433.23</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>68.78</v>
+        <v>69.04000000000001</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>470.72</v>
+        <v>472.53</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>332.52</v>
+        <v>333.79</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>520.08</v>
+        <v>522.0700000000001</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>166.39</v>
+        <v>167.03</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>3928.02</v>
+        <v>3943.09</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>498.78</v>
+        <v>500.69</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>530.08</v>
+        <v>532.11</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>189.1</v>
+        <v>189.82</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>184.44</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>662.4400000000001</v>
+        <v>664.98</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>783.88</v>
+        <v>786.89</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1276.55</v>
+        <v>1281.45</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>1113.93</v>
+        <v>1118.21</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>761.8</v>
+        <v>764.73</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>554.63</v>
+        <v>556.76</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>354.6</v>
+        <v>355.96</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>223.28</v>
+        <v>224.14</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>201.33</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>6681.47</v>
+        <v>6707.11</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>206.65</v>
+        <v>207.44</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>675.96</v>
+        <v>678.5599999999999</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>900.91</v>
+        <v>904.37</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>249.39</v>
+        <v>250.35</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>268.87</v>
+        <v>269.9</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>58680.2</v>
+        <v>58905.43</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>174.57</v>
+        <v>175.24</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>165.53</v>
+        <v>166.17</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>481.89</v>
+        <v>483.74</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>107.67</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>72.28</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>35256.81</v>
+        <v>35392.14</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>992.88</v>
+        <v>996.6900000000001</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>2439.33</v>
+        <v>2448.69</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>1091.07</v>
+        <v>1095.26</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>150.8</v>
+        <v>151.38</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>525.14</v>
+        <v>527.16</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>102.77</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>366.81</v>
+        <v>368.47</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>714.91</v>
+        <v>718.15</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>756.48</v>
+        <v>759.9</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>94.56</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>128.98</v>
+        <v>129.56</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>831.29</v>
+        <v>835.0599999999999</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1088.45</v>
+        <v>1093.38</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>96406.22</v>
+        <v>96843.10000000001</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>27420.02</v>
+        <v>27544.28</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>240.95</v>
+        <v>242.04</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>602.3</v>
+        <v>605.03</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>275.89</v>
+        <v>277.14</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>45.98</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>4711.69</v>
+        <v>4733.04</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>222.84</v>
+        <v>223.85</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>10519.03</v>
+        <v>10566.7</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>384.79</v>
+        <v>386.53</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>498.78</v>
+        <v>501.04</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>290.69</v>
+        <v>292.01</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>556.45</v>
+        <v>558.97</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>325.24</v>
+        <v>326.72</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>1617.28</v>
+        <v>1624.61</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>6878.95</v>
+        <v>6910.12</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1309.01</v>
+        <v>1314.95</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>321.23</v>
+        <v>322.69</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>291.47</v>
+        <v>292.79</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>294.15</v>
+        <v>295.48</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>320.31</v>
+        <v>321.76</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>667.3099999999999</v>
+        <v>670.33</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>13991.7</v>
+        <v>14055.11</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>124.69</v>
+        <v>125.26</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>27423.76</v>
+        <v>27548.04</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>783.84</v>
+        <v>787.4</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>5329</v>
+        <v>5353.15</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>97.09</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2515.42</v>
+        <v>2526.82</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1485.94</v>
+        <v>1492.67</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>310.7</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2682.09</v>
+        <v>2694.24</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>480.07</v>
+        <v>482.25</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>310.7</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>695.5599999999999</v>
+        <v>698.71</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>2208.12</v>
+        <v>2213.98</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>507.22</v>
+        <v>508.56</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>331.09</v>
+        <v>331.97</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>341.93</v>
+        <v>342.84</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2165.55</v>
+        <v>2171.29</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>332.52</v>
+        <v>333.4</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>599.4400000000001</v>
+        <v>601.03</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>445.78</v>
+        <v>446.96</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>662.1900000000001</v>
+        <v>663.9400000000001</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>618.27</v>
+        <v>619.91</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>146.31</v>
+        <v>146.7</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>550.21</v>
+        <v>551.67</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1673.51</v>
+        <v>1677.95</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>276.66</v>
+        <v>277.4</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>1521.65</v>
+        <v>1525.68</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>414.39</v>
+        <v>415.49</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>575.39</v>
+        <v>576.92</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>974.7</v>
+        <v>977.28</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>240.95</v>
+        <v>241.58</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>463.71</v>
+        <v>464.94</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1857.42</v>
+        <v>1862.35</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>178.55</v>
+        <v>179.02</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2678.19</v>
+        <v>2685.29</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>419.41</v>
+        <v>420.52</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>8071.91</v>
+        <v>8093.32</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>4444.85</v>
+        <v>4456.64</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1170.29</v>
+        <v>1173.39</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>441.62</v>
+        <v>442.8</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>33982.9</v>
+        <v>34073.01</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>118.2</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>107.59</v>
+        <v>107.87</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1068.74</v>
+        <v>1071.57</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>12635.76</v>
+        <v>12669.26</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>451.5</v>
+        <v>452.69</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>771.09</v>
+        <v>773.13</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1857.42</v>
+        <v>1862.35</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>16367.04</v>
+        <v>16410.44</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>1341.63</v>
+        <v>1345.19</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>323.17</v>
+        <v>324.02</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>179.81</v>
+        <v>180.29</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>1390.37</v>
+        <v>1394.06</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>17089.57</v>
+        <v>17134.89</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>557.23</v>
+        <v>558.7</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>32892.65</v>
+        <v>32979.87</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>148.59</v>
+        <v>148.99</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>891.29</v>
+        <v>893.66</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>112.61</v>
+        <v>112.91</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>883.25</v>
+        <v>885.59</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>120.47</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1039.12</v>
+        <v>1041.87</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>178.55</v>
+        <v>179.02</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>65.45999999999999</v>
+        <v>65.64</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>203.28</v>
+        <v>203.82</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>141.84</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>60.59</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>1530.1</v>
+        <v>1534.16</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>662.4400000000001</v>
+        <v>664.1900000000001</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1005.35</v>
+        <v>1008.01</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>138.66</v>
+        <v>139.02</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1114.45</v>
+        <v>1117.41</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>2891.34</v>
+        <v>2899.01</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>60.98</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>3016.04</v>
+        <v>3011.8</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>124.69</v>
+        <v>124.52</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1149.52</v>
+        <v>1147.91</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>529.95</v>
+        <v>529.21</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>629.83</v>
+        <v>628.95</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2582.52</v>
+        <v>2578.89</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>364.73</v>
+        <v>364.22</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2361.13</v>
+        <v>2357.82</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>82.53</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>742.97</v>
+        <v>741.9299999999999</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>454.61</v>
+        <v>453.98</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>261.86</v>
+        <v>261.49</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>174.57</v>
+        <v>174.33</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>1196.28</v>
+        <v>1194.6</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>1114.45</v>
+        <v>1112.89</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1109.26</v>
+        <v>1107.7</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>4902.58</v>
+        <v>4895.7</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2571.67</v>
+        <v>2568.06</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>129.76</v>
+        <v>129.58</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>165.91</v>
+        <v>165.67</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>3400.18</v>
+        <v>3395.41</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>557.4</v>
+        <v>556.61</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>73.73999999999999</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>86.38</v>
+        <v>86.26000000000001</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>10366.34</v>
+        <v>10351.8</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>332.52</v>
+        <v>332.05</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>992.4400000000001</v>
+        <v>991.05</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>3581.83</v>
+        <v>3576.81</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>1483.99</v>
+        <v>1481.91</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>544.54</v>
+        <v>543.77</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1340.98</v>
+        <v>1339.1</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>1067.17</v>
+        <v>1065.68</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>21168.24</v>
+        <v>21138.54</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>492.92</v>
+        <v>492.23</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>748.16</v>
+        <v>747.11</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>276.85</v>
+        <v>276.46</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>510.08</v>
+        <v>509.36</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>725.3</v>
+        <v>724.29</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>138.66</v>
+        <v>138.46</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>477.99</v>
+        <v>477.32</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>133.01</v>
+        <v>132.82</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>159.93</v>
+        <v>159.71</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>357.09</v>
+        <v>356.59</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>4166.86</v>
+        <v>4161.01</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>644.25</v>
+        <v>643.35</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>1453.57</v>
+        <v>1451.53</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>481.89</v>
+        <v>481.21</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>13750.23</v>
+        <v>13730.94</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>790.5700000000001</v>
+        <v>789.46</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1721.06</v>
+        <v>1718.65</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>143.53</v>
+        <v>143.33</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>2357.16</v>
+        <v>2353.86</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>80.01000000000001</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>216.9</v>
+        <v>217.18</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1766.78</v>
+        <v>1769.05</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>5922.96</v>
+        <v>5930.56</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>631.78</v>
+        <v>632.59</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1184.59</v>
+        <v>1186.11</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>594.63</v>
+        <v>595.4</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>346.03</v>
+        <v>346.47</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>542.9</v>
+        <v>543.6</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>21813.95</v>
+        <v>21841.92</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>606.05</v>
+        <v>606.83</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>74</v>
+        <v>74.09</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1492.03</v>
+        <v>1493.94</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>2183.02</v>
+        <v>2185.82</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>161.06</v>
+        <v>161.27</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>379.57</v>
+        <v>380.06</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>542.42</v>
+        <v>543.11</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>694.13</v>
+        <v>695.02</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>183.95</v>
+        <v>184.19</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1736.13</v>
+        <v>1738.36</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>882.21</v>
+        <v>883.34</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>55.74</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>872.86</v>
+        <v>873.98</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>2252.28</v>
+        <v>2255.17</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>495.5</v>
+        <v>496.14</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>4585.1</v>
+        <v>4590.98</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>243.93</v>
+        <v>244.25</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>5193.79</v>
+        <v>5200.45</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>5992.14</v>
+        <v>5999.82</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>6047.37</v>
+        <v>6055.12</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>168.66</v>
+        <v>168.88</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>289.76</v>
+        <v>290.14</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>873.0599999999999</v>
+        <v>874.17</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>9911.42</v>
+        <v>9924.120000000001</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>99.69</v>
+        <v>99.81999999999999</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>1925.03</v>
+        <v>1927.5</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>192.76</v>
+        <v>193</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>1857.42</v>
+        <v>1859.8</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>227.96</v>
+        <v>228.25</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>722.84</v>
+        <v>723.76</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>2168.51</v>
+        <v>2171.29</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>1927.56</v>
+        <v>1930.03</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>2842.63</v>
+        <v>2846.28</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>3046.95</v>
+        <v>3067.92</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>102.94</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2369.19</v>
+        <v>2385.49</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>440.72</v>
+        <v>443.75</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>578</v>
+        <v>581.98</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>1911.97</v>
+        <v>1925.13</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>429.87</v>
+        <v>432.83</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>483.19</v>
+        <v>486.52</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>2342.97</v>
+        <v>2359.1</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>1659.91</v>
+        <v>1671.34</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>2173.35</v>
+        <v>2188.31</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1102.76</v>
+        <v>1110.35</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2095.4</v>
+        <v>2109.83</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>856.3099999999999</v>
+        <v>862.2</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>563.14</v>
+        <v>567.01</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>669.1900000000001</v>
+        <v>673.8</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>102.94</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>24768.64</v>
+        <v>24939.13</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>411.49</v>
+        <v>414.32</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>589.63</v>
+        <v>593.6900000000001</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>6054.27</v>
+        <v>6095.94</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>130.02</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>119.63</v>
+        <v>120.45</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>1531</v>
+        <v>1541.53</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>324.4</v>
+        <v>326.63</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>1559.49</v>
+        <v>1570.22</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>2058.75</v>
+        <v>2072.92</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1472.95</v>
+        <v>1483.09</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>551.77</v>
+        <v>555.5700000000001</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>14248.07</v>
+        <v>14346.14</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1062.27</v>
+        <v>1069.58</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>2594.34</v>
+        <v>2612.2</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>2162.66</v>
+        <v>2177.55</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>360.05</v>
+        <v>363.13</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>31705.91</v>
+        <v>31976.86</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>748.16</v>
+        <v>754.5599999999999</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>7217.18</v>
+        <v>7278.86</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>205.87</v>
+        <v>207.63</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>708.6799999999999</v>
+        <v>714.73</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>5503.45</v>
+        <v>5550.48</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>1726.26</v>
+        <v>1741.02</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>638.28</v>
+        <v>643.73</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>205.87</v>
+        <v>207.63</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>411.75</v>
+        <v>415.27</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>182.88</v>
+        <v>184.45</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>658.8</v>
+        <v>664.4299999999999</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>242.32</v>
+        <v>244.39</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>129.76</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>1356.05</v>
+        <v>1367.64</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>289.33</v>
+        <v>291.8</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>394.86</v>
+        <v>398.24</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>656.59</v>
+        <v>662.2</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>406.81</v>
+        <v>410.29</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>437.73</v>
+        <v>441.47</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>1837.94</v>
+        <v>1853.64</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>110.62</v>
+        <v>111.57</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>430.19</v>
+        <v>433.87</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>3476.05</v>
+        <v>3505.76</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>4112.43</v>
+        <v>4147.58</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>823.5</v>
+        <v>830.54</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>598.53</v>
+        <v>603.65</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>60.01</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>280.75</v>
+        <v>283.15</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>1061.2</v>
+        <v>1070.27</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>403.26</v>
+        <v>406.7</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>691.01</v>
+        <v>696.92</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>856.13</v>
+        <v>863.4400000000001</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>350.18</v>
+        <v>353.17</v>
       </c>
     </row>
     <row r="751">
@@ -46262,7 +46262,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>9916.08</v>
+        <v>10000.82</v>
       </c>
     </row>
     <row r="752">
@@ -46323,7 +46323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>1274.18</v>
+        <v>1285.07</v>
       </c>
     </row>
     <row r="753">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>573.59</v>
+        <v>578.49</v>
       </c>
     </row>
     <row r="754">
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>3245</v>
+        <v>3272.74</v>
       </c>
     </row>
     <row r="755">
@@ -46506,7 +46506,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>779.29</v>
+        <v>785.95</v>
       </c>
     </row>
     <row r="756">
@@ -46567,7 +46567,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>4987.76</v>
+        <v>5030.38</v>
       </c>
     </row>
     <row r="757">
@@ -46628,7 +46628,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>1708.77</v>
+        <v>1723.38</v>
       </c>
     </row>
     <row r="758">
@@ -46689,7 +46689,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>548.65</v>
+        <v>553.34</v>
       </c>
     </row>
     <row r="759">
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>2662.74</v>
+        <v>2685.49</v>
       </c>
     </row>
     <row r="760">
@@ -46811,7 +46811,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>526.05</v>
+        <v>530.55</v>
       </c>
     </row>
     <row r="761">
@@ -46872,7 +46872,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>183.79</v>
+        <v>185.36</v>
       </c>
     </row>
     <row r="762">
@@ -46933,7 +46933,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>494.1</v>
+        <v>498.32</v>
       </c>
     </row>
     <row r="763">
@@ -46994,7 +46994,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>1165.11</v>
+        <v>1175.07</v>
       </c>
     </row>
     <row r="764">
@@ -47055,7 +47055,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>776.74</v>
+        <v>783.38</v>
       </c>
     </row>
     <row r="765">
@@ -47116,7 +47116,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>391.75</v>
+        <v>395.09</v>
       </c>
     </row>
     <row r="766">
@@ -47177,7 +47177,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>1730.13</v>
+        <v>1744.91</v>
       </c>
     </row>
     <row r="767">
@@ -47238,7 +47238,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>194.64</v>
+        <v>196.3</v>
       </c>
     </row>
     <row r="768">
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>865.0599999999999</v>
+        <v>872.46</v>
       </c>
     </row>
     <row r="769">
@@ -47360,7 +47360,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>280.04</v>
+        <v>282.44</v>
       </c>
     </row>
     <row r="770">
@@ -47421,7 +47421,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>30405.7</v>
+        <v>30665.54</v>
       </c>
     </row>
     <row r="771">
@@ -47482,7 +47482,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>29972.27</v>
+        <v>30228.41</v>
       </c>
     </row>
     <row r="772">
@@ -47543,7 +47543,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>459.81</v>
+        <v>463.74</v>
       </c>
     </row>
     <row r="773">
@@ -47604,7 +47604,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>2992.66</v>
+        <v>3024.76</v>
       </c>
     </row>
     <row r="774">
@@ -47665,7 +47665,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>3269</v>
+        <v>3304.06</v>
       </c>
     </row>
     <row r="775">
@@ -47726,7 +47726,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>12098.99</v>
+        <v>12228.77</v>
       </c>
     </row>
     <row r="776">
@@ -47787,7 +47787,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>894.48</v>
+        <v>904.0700000000001</v>
       </c>
     </row>
     <row r="777">
@@ -47848,7 +47848,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>247.05</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="778">
@@ -47909,7 +47909,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>1409.3</v>
+        <v>1424.42</v>
       </c>
     </row>
     <row r="779">
@@ -47970,7 +47970,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>168.82</v>
+        <v>170.63</v>
       </c>
     </row>
     <row r="780">
@@ -48031,7 +48031,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>1246.94</v>
+        <v>1260.32</v>
       </c>
     </row>
     <row r="781">
@@ -48092,7 +48092,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>370.57</v>
+        <v>374.55</v>
       </c>
     </row>
     <row r="782">
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>2415.95</v>
+        <v>2441.86</v>
       </c>
     </row>
     <row r="783">
@@ -48214,7 +48214,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>425.47</v>
+        <v>430.04</v>
       </c>
     </row>
     <row r="784">
@@ -48275,7 +48275,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>7022.12</v>
+        <v>7097.44</v>
       </c>
     </row>
     <row r="785">
@@ -48336,7 +48336,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>17909.76</v>
+        <v>18101.87</v>
       </c>
     </row>
     <row r="786">
@@ -48397,7 +48397,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>198.28</v>
+        <v>200.4</v>
       </c>
     </row>
     <row r="787">
@@ -48458,7 +48458,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>166.53</v>
+        <v>168.32</v>
       </c>
     </row>
     <row r="788">
@@ -48519,7 +48519,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>1084.84</v>
+        <v>1096.47</v>
       </c>
     </row>
     <row r="789">
@@ -48580,7 +48580,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>10398.31</v>
+        <v>10509.85</v>
       </c>
     </row>
     <row r="790">
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>661.66</v>
+        <v>668.75</v>
       </c>
     </row>
     <row r="791">
@@ -48702,7 +48702,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>1150.76</v>
+        <v>1163.1</v>
       </c>
     </row>
     <row r="792">
@@ -48763,7 +48763,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>370.99</v>
+        <v>374.97</v>
       </c>
     </row>
     <row r="793">
@@ -48824,7 +48824,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>274.33</v>
+        <v>277.27</v>
       </c>
     </row>
     <row r="794">
@@ -48885,7 +48885,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>1464.18</v>
+        <v>1482.17</v>
       </c>
     </row>
     <row r="795">
@@ -48946,7 +48946,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>4104.51</v>
+        <v>4154.95</v>
       </c>
     </row>
     <row r="796">
@@ -49007,7 +49007,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>190.68</v>
+        <v>193.02</v>
       </c>
     </row>
     <row r="797">
@@ -49068,7 +49068,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>1101.46</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="798">
@@ -49129,7 +49129,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>67.61</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="799">
@@ -49190,7 +49190,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>1084.84</v>
+        <v>1098.17</v>
       </c>
     </row>
     <row r="800">
@@ -49251,7 +49251,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>991.58</v>
+        <v>1003.76</v>
       </c>
     </row>
     <row r="801">
@@ -49312,7 +49312,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>477.99</v>
+        <v>483.87</v>
       </c>
     </row>
     <row r="802">
@@ -49373,7 +49373,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>40.27</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="803">
@@ -49434,7 +49434,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>800.12</v>
+        <v>809.95</v>
       </c>
     </row>
     <row r="804">
@@ -49495,7 +49495,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>2728.85</v>
+        <v>2762.39</v>
       </c>
     </row>
     <row r="805">
@@ -49556,7 +49556,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>321.87</v>
+        <v>325.82</v>
       </c>
     </row>
     <row r="806">
@@ -49617,7 +49617,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>194.18</v>
+        <v>196.57</v>
       </c>
     </row>
     <row r="807">
@@ -49678,7 +49678,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>1039.12</v>
+        <v>1051.89</v>
       </c>
     </row>
     <row r="808">
@@ -49739,7 +49739,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>567.36</v>
+        <v>574.33</v>
       </c>
     </row>
     <row r="809">
@@ -49800,7 +49800,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>656.59</v>
+        <v>664.66</v>
       </c>
     </row>
     <row r="810">
@@ -49861,7 +49861,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>1102.76</v>
+        <v>1116.32</v>
       </c>
     </row>
     <row r="811">
@@ -49922,7 +49922,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>136.38</v>
+        <v>138.06</v>
       </c>
     </row>
     <row r="812">
@@ -49983,7 +49983,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>1188.75</v>
+        <v>1203.36</v>
       </c>
     </row>
     <row r="813">
@@ -50044,7 +50044,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>5457.15</v>
+        <v>5524.22</v>
       </c>
     </row>
     <row r="814">
@@ -50105,7 +50105,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>918.97</v>
+        <v>930.26</v>
       </c>
     </row>
     <row r="815">
@@ -50166,7 +50166,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>158.21</v>
+        <v>160.15</v>
       </c>
     </row>
     <row r="816">
@@ -50227,7 +50227,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>441.1</v>
+        <v>446.53</v>
       </c>
     </row>
     <row r="817">
@@ -50288,7 +50288,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>1042.26</v>
+        <v>1055.07</v>
       </c>
     </row>
     <row r="818">
@@ -50349,7 +50349,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>404.48</v>
+        <v>409.67</v>
       </c>
     </row>
     <row r="819">
@@ -50410,7 +50410,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>265.75</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="820">
@@ -50471,7 +50471,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>310.05</v>
+        <v>314.03</v>
       </c>
     </row>
     <row r="821">
@@ -50532,7 +50532,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>503.19</v>
+        <v>509.66</v>
       </c>
     </row>
     <row r="822">
@@ -50593,7 +50593,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>310.05</v>
+        <v>314.03</v>
       </c>
     </row>
     <row r="823">
@@ -50654,7 +50654,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>766.35</v>
+        <v>776.2</v>
       </c>
     </row>
     <row r="824">
@@ -50715,7 +50715,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>613.08</v>
+        <v>620.96</v>
       </c>
     </row>
     <row r="825">
@@ -50776,7 +50776,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>646.85</v>
+        <v>655.16</v>
       </c>
     </row>
     <row r="826">
@@ -50837,7 +50837,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>1108.22</v>
+        <v>1122.46</v>
       </c>
     </row>
     <row r="827">
@@ -50898,7 +50898,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>186.07</v>
+        <v>188.47</v>
       </c>
     </row>
     <row r="828">
@@ -50959,7 +50959,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>1067.17</v>
+        <v>1080.89</v>
       </c>
     </row>
     <row r="829">
@@ -51020,7 +51020,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>689.97</v>
+        <v>698.84</v>
       </c>
     </row>
     <row r="830">
@@ -51081,7 +51081,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>540.86</v>
+        <v>547.8099999999999</v>
       </c>
     </row>
     <row r="831">
@@ -51142,7 +51142,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>540.86</v>
+        <v>547.8099999999999</v>
       </c>
     </row>
     <row r="832">
@@ -51203,7 +51203,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>331.26</v>
+        <v>335.51</v>
       </c>
     </row>
     <row r="833">
@@ -51264,7 +51264,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>1694.28</v>
+        <v>1716.05</v>
       </c>
     </row>
     <row r="834">
@@ -51325,7 +51325,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>867.8</v>
+        <v>878.95</v>
       </c>
     </row>
     <row r="835">
@@ -51386,7 +51386,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>617.8099999999999</v>
+        <v>625.75</v>
       </c>
     </row>
     <row r="836">
@@ -51447,7 +51447,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>928.85</v>
+        <v>940.79</v>
       </c>
     </row>
     <row r="837">
@@ -51508,7 +51508,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>182.36</v>
+        <v>184.71</v>
       </c>
     </row>
     <row r="838">
@@ -51569,7 +51569,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>706.6</v>
+        <v>715.6799999999999</v>
       </c>
     </row>
     <row r="839">
@@ -51630,7 +51630,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>1894.45</v>
+        <v>1918.8</v>
       </c>
     </row>
     <row r="840">
@@ -51691,7 +51691,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>688.54</v>
+        <v>697.39</v>
       </c>
     </row>
     <row r="841">
@@ -51752,7 +51752,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>16372.83</v>
+        <v>16583.22</v>
       </c>
     </row>
     <row r="842">
@@ -51813,7 +51813,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>376.16</v>
+        <v>380.99</v>
       </c>
     </row>
     <row r="843">
@@ -51874,7 +51874,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>1100.94</v>
+        <v>1115.09</v>
       </c>
     </row>
     <row r="844">
@@ -51935,7 +51935,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>4377.28</v>
+        <v>4433.52</v>
       </c>
     </row>
     <row r="845">
@@ -51996,7 +51996,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>29304.2</v>
+        <v>29680.75</v>
       </c>
     </row>
     <row r="846">
@@ -52057,7 +52057,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>7181.09</v>
+        <v>7273.36</v>
       </c>
     </row>
     <row r="847">
@@ -52118,7 +52118,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>1033.92</v>
+        <v>1047.21</v>
       </c>
     </row>
     <row r="848">
@@ -52179,7 +52179,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>1227.46</v>
+        <v>1243.23</v>
       </c>
     </row>
     <row r="849">
@@ -52240,7 +52240,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>1374.75</v>
+        <v>1392.42</v>
       </c>
     </row>
     <row r="850">
@@ -52301,7 +52301,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>490.98</v>
+        <v>497.29</v>
       </c>
     </row>
     <row r="851">
@@ -52362,7 +52362,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>1031.48</v>
+        <v>1044.73</v>
       </c>
     </row>
     <row r="852">
@@ -52423,7 +52423,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>706.6</v>
+        <v>715.6799999999999</v>
       </c>
     </row>
     <row r="853">
@@ -52484,7 +52484,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>4507.17</v>
+        <v>4565.08</v>
       </c>
     </row>
     <row r="854">
@@ -52545,7 +52545,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>901.4299999999999</v>
+        <v>913.02</v>
       </c>
     </row>
     <row r="855">
@@ -52606,7 +52606,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>143.66</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="856">
@@ -52667,7 +52667,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>1180.7</v>
+        <v>1195.87</v>
       </c>
     </row>
     <row r="857">
@@ -52728,7 +52728,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>2564.02</v>
+        <v>2578.04</v>
       </c>
     </row>
     <row r="858">
@@ -52789,7 +52789,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>1954.6</v>
+        <v>1965.29</v>
       </c>
     </row>
     <row r="859">
@@ -52850,7 +52850,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>154.7</v>
+        <v>155.54</v>
       </c>
     </row>
     <row r="860">
@@ -52911,7 +52911,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>2096.66</v>
+        <v>2108.12</v>
       </c>
     </row>
     <row r="861">
@@ -52972,7 +52972,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>118.07</v>
+        <v>118.72</v>
       </c>
     </row>
     <row r="862">
@@ -53033,7 +53033,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>305.38</v>
+        <v>307.05</v>
       </c>
     </row>
     <row r="863">
@@ -53094,7 +53094,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>1574.26</v>
+        <v>1582.87</v>
       </c>
     </row>
     <row r="864">
@@ -53155,7 +53155,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>1468.15</v>
+        <v>1476.18</v>
       </c>
     </row>
     <row r="865">
@@ -53216,7 +53216,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>7870.91</v>
+        <v>7913.95</v>
       </c>
     </row>
     <row r="866">
@@ -53277,7 +53277,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>108.74</v>
+        <v>109.34</v>
       </c>
     </row>
     <row r="867">
@@ -53338,7 +53338,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>273.55</v>
+        <v>275.04</v>
       </c>
     </row>
     <row r="868">
@@ -53399,7 +53399,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>111.23</v>
+        <v>111.84</v>
       </c>
     </row>
     <row r="869">
@@ -53460,7 +53460,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>602.04</v>
+        <v>605.33</v>
       </c>
     </row>
     <row r="870">
@@ -53521,7 +53521,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>4925.41</v>
+        <v>4952.35</v>
       </c>
     </row>
     <row r="871">
@@ -53582,7 +53582,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>158.52</v>
+        <v>159.38</v>
       </c>
     </row>
     <row r="872">
@@ -53643,7 +53643,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>903.62</v>
+        <v>908.5599999999999</v>
       </c>
     </row>
     <row r="873">
@@ -53704,7 +53704,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>1636.61</v>
+        <v>1645.56</v>
       </c>
     </row>
     <row r="874">
@@ -53765,7 +53765,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>2057.45</v>
+        <v>2068.7</v>
       </c>
     </row>
     <row r="875">
@@ -53826,7 +53826,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>1259.41</v>
+        <v>1266.3</v>
       </c>
     </row>
     <row r="876">
@@ -53887,7 +53887,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>3520.53</v>
+        <v>3539.78</v>
       </c>
     </row>
     <row r="877">
@@ -53948,7 +53948,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>11292.27</v>
+        <v>11354.03</v>
       </c>
     </row>
     <row r="878">
@@ -54009,7 +54009,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>6235.61</v>
+        <v>6269.71</v>
       </c>
     </row>
     <row r="879">
@@ -54070,7 +54070,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>26493.57</v>
+        <v>26638.46</v>
       </c>
     </row>
     <row r="880">
@@ -54131,7 +54131,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>82.09</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="881">
@@ -54192,7 +54192,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>1344.36</v>
+        <v>1351.71</v>
       </c>
     </row>
     <row r="882">
@@ -54253,7 +54253,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>879.09</v>
+        <v>883.9</v>
       </c>
     </row>
     <row r="883">
@@ -54314,7 +54314,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>539.54</v>
+        <v>542.49</v>
       </c>
     </row>
     <row r="884">
@@ -54375,7 +54375,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>439.55</v>
+        <v>441.95</v>
       </c>
     </row>
     <row r="885">
@@ -54436,7 +54436,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>8416.84</v>
+        <v>8462.870000000001</v>
       </c>
     </row>
     <row r="886">
@@ -54497,7 +54497,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>654.64</v>
+        <v>658.22</v>
       </c>
     </row>
     <row r="887">
@@ -54558,7 +54558,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>1193.94</v>
+        <v>1200.47</v>
       </c>
     </row>
     <row r="888">
@@ -54619,7 +54619,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>782.52</v>
+        <v>786.8</v>
       </c>
     </row>
     <row r="889">
@@ -54680,7 +54680,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>1952.72</v>
+        <v>1963.4</v>
       </c>
     </row>
     <row r="890">
@@ -54741,7 +54741,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>994.95</v>
+        <v>1000.4</v>
       </c>
     </row>
     <row r="891">
@@ -54802,7 +54802,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>994.95</v>
+        <v>1000.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/dic-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30393,7 +30393,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31114,7 +31114,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34774,7 +34774,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -35689,7 +35689,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -36238,7 +36238,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38556,7 +38556,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40386,7 +40386,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -42338,7 +42338,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42460,7 +42460,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -43985,7 +43985,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45815,7 +45815,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47584,7 +47584,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -47645,7 +47645,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -48011,7 +48011,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48072,7 +48072,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -48255,7 +48255,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48743,7 +48743,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -49353,7 +49353,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -49414,7 +49414,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -50817,7 +50817,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -50939,7 +50939,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -52159,7 +52159,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -52220,7 +52220,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -52281,7 +52281,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -52342,7 +52342,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -53013,7 +53013,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -53440,7 +53440,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -53501,7 +53501,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -53867,7 +53867,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -54050,7 +54050,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -54172,7 +54172,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -54294,7 +54294,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -54599,7 +54599,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/dic-2025.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/dic-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIa. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PREFECTURA AEREA DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Concepción" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE AYSEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ESCUELA DE SUBOFICIALES GRUPO ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIRECCIÓN GENERAL DE CARABINEROS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Comandancia Base Naval Iquique</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DELEGACION PRESIDENCIAL PROVINCIAL DE LOS ANDES</t>
+          <t>GOBERNACION PROVINCIAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tribunal de Juicio Oral en lo Pena de Talca</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE VALPARAISO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR SERVICIO SALUD ACONCAGUA</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ESCUELA DE FORMACIÓN DE CARABINEROS LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DELEGACION PRESIDENCIAL REGIONAL DE LA ARAUCANIA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Antofagasta" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Coyhaique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Juzgado de Familia de Coyhaique</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN - SEMC</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CCP Linares</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16465,12 +16465,12 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Protección</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Regimiento de Infantería N° 23 "Copiapó"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DIRECCION DE INVESTIGACION, DESARROLLO DE LA ARMA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR SALUD MUNICIPAL</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Secretaria Ministerial de Educación Región Ñuble</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20613,7 +20613,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21467,7 +21467,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CCP Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21711,7 +21711,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21772,7 +21772,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales X Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>ASEMUCH SANTA JUANA</t>
+          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Villarrica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23419,7 +23419,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -23541,7 +23541,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24334,7 +24334,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24517,12 +24517,12 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25127,7 +25127,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR DEL PERSONAL CMPA</t>
+          <t>I MUNICIPALIDAD DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>CORP MUNIC DE QUELLON PARA LA EDUC SALUD</t>
+          <t>Corporación Municipal de Quellón</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -26469,7 +26469,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -26652,7 +26652,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valdivia" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -27628,12 +27628,12 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Protección</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -28055,7 +28055,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Juzgado de Letras del Trabajo de Castro</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28177,7 +28177,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -28299,7 +28299,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28360,7 +28360,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -28970,7 +28970,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DIVISIÓN DE BIENESTAR SOCIAL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29031,7 +29031,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Concepción</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29336,7 +29336,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -29885,7 +29885,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -29946,7 +29946,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30068,7 +30068,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -30129,7 +30129,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>Iª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30190,7 +30190,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -30251,7 +30251,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -30312,7 +30312,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Juzgado de Familia de Ancud</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -30987,7 +30987,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -31048,7 +31048,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -31231,7 +31231,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -31648,7 +31648,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -31841,7 +31841,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -32207,7 +32207,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -32329,7 +32329,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -32390,7 +32390,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Angol</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32878,7 +32878,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -32939,7 +32939,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Chile Chico</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33122,7 +33122,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -33427,7 +33427,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33549,7 +33549,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TORTEL</t>
+          <t>Ilustre Municipalidad de Tortel</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -33610,7 +33610,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar La Reina</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Instituto de Desarrollo Agropecuario</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34159,7 +34159,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -34220,7 +34220,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -35623,7 +35623,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Curacautín</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35684,7 +35684,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -35745,7 +35745,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE IQUIQUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -36111,7 +36111,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Prisión Arica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -36782,12 +36782,12 @@
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Protección</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36843,7 +36843,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -36904,7 +36904,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -37026,7 +37026,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Zona de Bienestar "Coyhaique"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -37514,7 +37514,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -37758,7 +37758,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Secretaría Ministerial de Educación - RM</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -37941,7 +37941,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -38063,7 +38063,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -38185,7 +38185,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -38368,7 +38368,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Camino La Pólvora</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>ESCUELA DE FORMACIÓN DE CARABINEROS LOS ANDES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -38551,7 +38551,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -38734,7 +38734,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -38795,7 +38795,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39344,7 +39344,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -39527,7 +39527,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Cochagua</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -39771,7 +39771,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -39954,7 +39954,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PESCA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION VI REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -40442,7 +40442,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CCP de Rengo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -40991,7 +40991,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41357,7 +41357,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -41418,7 +41418,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA CAMPO MILITAR PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -41601,7 +41601,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO ECO</t>
+          <t>CORPORACION MUNICIPAL DE FOMENTO AL DESARROLLO ECONOMICO Y PRODUCTIVO</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -41723,7 +41723,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -42384,7 +42384,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
@@ -42394,7 +42394,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>BASE NAVAL PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>DESTACAMENTO IM Nº 1 LYNCH</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -43187,7 +43187,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -43614,7 +43614,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -43797,12 +43797,12 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -44529,7 +44529,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -44590,7 +44590,7 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>- - -</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -44773,7 +44773,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -44956,7 +44956,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Coyhaique" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -45139,7 +45139,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -45261,7 +45261,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -45322,7 +45322,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -45383,7 +45383,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -45505,7 +45505,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -45688,7 +45688,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO BIENESTAR SOCIAL IIA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -45749,7 +45749,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -46176,7 +46176,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -46359,7 +46359,7 @@
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -46481,12 +46481,12 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -46664,7 +46664,7 @@
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -46725,7 +46725,7 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -46847,7 +46847,7 @@
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -46969,7 +46969,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -47030,7 +47030,7 @@
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -47091,7 +47091,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -47213,7 +47213,7 @@
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -47518,7 +47518,7 @@
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -47579,7 +47579,7 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -47701,7 +47701,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -47762,7 +47762,7 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -47823,7 +47823,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -48250,7 +48250,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -48311,7 +48311,7 @@
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -48372,7 +48372,7 @@
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -48433,7 +48433,7 @@
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -48728,7 +48728,7 @@
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
@@ -48799,7 +48799,7 @@
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -48982,7 +48982,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Chiloé</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
@@ -49470,7 +49470,7 @@
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -49531,7 +49531,7 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H805" t="inlineStr">
@@ -49592,7 +49592,7 @@
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H806" t="inlineStr">
@@ -49653,7 +49653,7 @@
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -49714,7 +49714,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
@@ -49775,7 +49775,7 @@
       </c>
       <c r="G809" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H809" t="inlineStr">
@@ -49836,7 +49836,7 @@
       </c>
       <c r="G810" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H810" t="inlineStr">
@@ -49897,7 +49897,7 @@
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile CET Antofagasta II Región</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H811" t="inlineStr">
@@ -49958,7 +49958,7 @@
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
@@ -50024,7 +50024,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50080,7 +50080,7 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H814" t="inlineStr">
@@ -50141,7 +50141,7 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H815" t="inlineStr">
@@ -50202,7 +50202,7 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>Escuela de Gendarmeria</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
@@ -50324,7 +50324,7 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H818" t="inlineStr">
@@ -50385,7 +50385,7 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H819" t="inlineStr">
@@ -50446,7 +50446,7 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H820" t="inlineStr">
@@ -50507,7 +50507,7 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H821" t="inlineStr">
@@ -50568,7 +50568,7 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
@@ -50629,7 +50629,7 @@
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>CET CPF Metropolitano</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -50690,7 +50690,7 @@
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>CET CPF Metropolitano</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
@@ -50802,7 +50802,7 @@
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -50812,7 +50812,7 @@
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
@@ -50924,7 +50924,7 @@
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
@@ -50934,7 +50934,7 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA TUMBES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
@@ -50995,7 +50995,7 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H829" t="inlineStr">
@@ -51056,7 +51056,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -51117,7 +51117,7 @@
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
@@ -51483,7 +51483,7 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H837" t="inlineStr">
@@ -51544,7 +51544,7 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H838" t="inlineStr">
@@ -51666,7 +51666,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -51910,7 +51910,7 @@
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
@@ -52093,7 +52093,7 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -52154,7 +52154,7 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
@@ -52215,7 +52215,7 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -52276,7 +52276,7 @@
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
@@ -52337,7 +52337,7 @@
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -52398,7 +52398,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H852" t="inlineStr">
@@ -52520,7 +52520,7 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
@@ -52642,7 +52642,7 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H856" t="inlineStr">
@@ -52703,7 +52703,7 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
@@ -52764,7 +52764,7 @@
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
@@ -52947,7 +52947,7 @@
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H861" t="inlineStr">
@@ -53252,7 +53252,7 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H866" t="inlineStr">
@@ -53313,7 +53313,7 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H867" t="inlineStr">
@@ -53618,7 +53618,7 @@
       </c>
       <c r="G872" t="inlineStr">
         <is>
-          <t>- - -</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H872" t="inlineStr">
@@ -53679,7 +53679,7 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>DEPTO HABITABILIDAD COMANDANCIA EN JEFE DE 1 Z. N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H873" t="inlineStr">
@@ -53984,7 +53984,7 @@
       </c>
       <c r="G878" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H878" t="inlineStr">
@@ -54157,7 +54157,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
@@ -54350,7 +54350,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CDP Talagante</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H884" t="inlineStr">
@@ -54533,7 +54533,7 @@
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
@@ -54777,7 +54777,7 @@
       </c>
       <c r="G891" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CCP Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H891" t="inlineStr">
